--- a/output/2026-09-07_20_Croazia_Zagrebacka_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-07_20_Croazia_Zagrebacka_Impiantistica_aspirazione_industriale.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Produttore leader croato di impianti climatizzazione/ventilazione industriale, camere bianche e filtrazione aria. Discrepanza minore su ragione sociale (d.d. vs d.o.o. in alcune fonti) da confermare in visura.</t>
+          <t>Produttore leader croato di impianti climatizzazione/ventilazione industriale, camere bianche e filtrazione aria. Discrepanza minore su ragione sociale (d.d. vs d.o.o. in alcune fonti) da confermare in visura. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Attivo dal 1993, produzione griglie/diffusori/filtri/ventilatori/UTA. Telefono da riconfermare (fonte registro imprese riporta numero diverso).</t>
+          <t>Attivo dal 1993, produzione griglie/diffusori/filtri/ventilatori/UTA. Telefono da riconfermare (fonte registro imprese riporta numero diverso). [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,7 +558,6 @@
           <t>Termovent d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Kerestinec, Sveta Nedelja, Zagrebačka županija</t>
@@ -611,11 +610,9 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Produzione filter bags per otprašivanje (dust collection), filtri per centrifughe e cabine di verniciatura. Sede legale a Zagreb ma stabilimento produttivo confermato a Kerestinec (contea). Contatti non confermati con certezza, lasciati vuoti.</t>
+          <t>Produzione filter bags per otprašivanje (dust collection), filtri per centrifughe e cabine di verniciatura. Sede legale a Zagreb ma stabilimento produttivo confermato a Kerestinec (contea). Contatti non confermati con certezza, lasciati vuoti. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -657,7 +654,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Distributore/rappresentante tecnologie industriali, produzione propria dust collector e sistemi trasporto materiali sfusi. Dati confermati da fonti multiple.</t>
+          <t>Distributore/rappresentante tecnologie industriali, produzione propria dust collector e sistemi trasporto materiali sfusi. Dati confermati da fonti multiple. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -699,7 +696,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Distributore/installatore sistemi di aspirazione centralizzata a marchio Aertecnica. Esiste anche un 'obrt' omonimo a indirizzo diverso, segnalato per chiarezza.</t>
+          <t>Distributore/installatore sistemi di aspirazione centralizzata a marchio Aertecnica. Esiste anche un 'obrt' omonimo a indirizzo diverso, segnalato per chiarezza. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
